--- a/frontend/public/data/faculty.xlsx
+++ b/frontend/public/data/faculty.xlsx
@@ -1729,7 +1729,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1789,7 +1789,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1827,7 +1827,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -2051,7 +2051,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -2256,7 +2256,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -2346,7 +2346,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -2862,7 +2862,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -2899,7 +2899,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -2936,7 +2936,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -2973,7 +2973,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -3010,7 +3010,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -3047,7 +3047,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -3086,7 +3086,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -3125,7 +3125,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -3164,7 +3164,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -3203,7 +3203,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -3238,7 +3238,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -3768,7 +3768,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -3805,7 +3805,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -3842,7 +3842,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -3879,7 +3879,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -3916,7 +3916,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -3953,7 +3953,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -3992,7 +3992,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -4031,7 +4031,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -4070,7 +4070,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -4109,7 +4109,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:t/>
+                    <a:t>None</a:t>
                   </a:r>
                 </a:p>
               </txPr>
@@ -4144,7 +4144,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -13400,7 +13400,7 @@
     <row r="2" ht="25" customHeight="1">
       <c r="A2" s="27" t="inlineStr">
         <is>
-          <t>共25个实训室方向 | 133位师资 | 覆盖来源/职称/级别/经验/认证/可用性/实训室匹配/教学管理/优先级等维度</t>
+          <t>共24个实训室方向 | 133位师资 | 覆盖来源/职称/级别/经验/认证/可用性/实训室匹配/教学管理/优先级等维度</t>
         </is>
       </c>
     </row>
@@ -13690,7 +13690,7 @@
 AIGC视觉传达实训室
 AI4S实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
@@ -13990,7 +13990,7 @@
 电子数据取证司法鉴定实训室
 AIGC视觉传达实训室
 AI4S实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
@@ -14142,7 +14142,7 @@
           <t>互联网舆情监测与管控实验室
 AIGC视觉传达实训室
 智能制造行业开发实训室
-鸿蒙智联实训室</t>
+鸿蒙物联网智能技术实训室</t>
         </is>
       </c>
       <c r="R8" s="7" t="inlineStr">
@@ -14303,7 +14303,7 @@
 AI高端装备制造实训室
 智能制造行业开发实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -15923,7 +15923,7 @@
 智能体实训室
 人工智能应用开发实训室
 数据标注实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -16079,7 +16079,7 @@
           <t>智能体实训室
 高性能智算实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R20" s="7" t="inlineStr">
@@ -16246,7 +16246,7 @@
         <is>
           <t>智能体实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
@@ -17823,7 +17823,7 @@
         <is>
           <t>低空智能实训室
 卫星互联网实训室
-空天地一体实训室
+虚拟仿真创新实训室
 智能交通行业应用开发实训室</t>
         </is>
       </c>
@@ -21136,7 +21136,7 @@
         <is>
           <t>具身智能实训室
 智能边缘计算应用开发实训室
-鸿蒙智联实训室</t>
+鸿蒙物联网智能技术实训室</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
@@ -21445,7 +21445,7 @@
           <t>具身智能实训室
 机器视觉和VLM实训室
 AIGC视觉传达实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 高性能智算实训室
 智能交通行业应用开发实训室
 人工智能应用开发实训室</t>
@@ -21757,7 +21757,7 @@
         <is>
           <t>低空智能实训室
 卫星互联网实训室
-空天地一体实训室
+虚拟仿真创新实训室
 人工智能应用开发实训室</t>
         </is>
       </c>
@@ -21910,8 +21910,8 @@
       <c r="Q58" s="30" t="inlineStr">
         <is>
           <t>卫星互联网实训室
-空天地一体实训室
-鸿蒙智联实训室</t>
+虚拟仿真创新实训室
+鸿蒙物联网智能技术实训室</t>
         </is>
       </c>
       <c r="R58" s="7" t="inlineStr">
@@ -22066,7 +22066,7 @@
       <c r="Q59" s="30" t="inlineStr">
         <is>
           <t>卫星互联网实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
@@ -22216,7 +22216,7 @@
         <is>
           <t>互联网舆情监测与管控实验室
 卫星互联网实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R60" s="7" t="inlineStr">
@@ -22366,7 +22366,7 @@
         <is>
           <t>AIGC视觉传达实训室
 卫星互联网实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
@@ -22517,7 +22517,7 @@
           <t>AIGC视觉传达实训室
 AI4S实训室
 卫星互联网实训室
-空天地一体实训室
+虚拟仿真创新实训室
 人工智能应用开发实训室</t>
         </is>
       </c>
@@ -22668,7 +22668,7 @@
         <is>
           <t>低空智能实训室
 卫星互联网实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R63" s="3" t="inlineStr">
@@ -22818,7 +22818,7 @@
         <is>
           <t>具身智能实训室
 卫星互联网实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R64" s="7" t="inlineStr">
@@ -22969,7 +22969,7 @@
           <t>互联网舆情监测与管控实验室
 AIGC视觉传达实训室
 卫星互联网实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R65" s="3" t="inlineStr">
@@ -23120,7 +23120,7 @@
           <t>AIGC视觉传达实训室
 AI4S实训室
 卫星互联网实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R66" s="7" t="inlineStr">
@@ -23269,7 +23269,7 @@
       <c r="Q67" s="30" t="inlineStr">
         <is>
           <t>卫星互联网实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R67" s="3" t="inlineStr">
@@ -23421,7 +23421,7 @@
 AIGC视觉传达实训室
 AI4S实训室
 卫星互联网实训室
-空天地一体实训室
+虚拟仿真创新实训室
 人工智能应用开发实训室</t>
         </is>
       </c>
@@ -23573,9 +23573,9 @@
           <t>具身智能实训室
 高性能智算实训室
 卫星互联网实训室
-空天地一体实训室
+虚拟仿真创新实训室
 TPU异构算力与软硬协同实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 人工智能应用开发实训室</t>
         </is>
       </c>
@@ -23728,7 +23728,7 @@
 AIGC视觉传达实训室
 AI4S实训室
 卫星互联网实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R70" s="7" t="inlineStr">
@@ -23877,7 +23877,7 @@
       <c r="Q71" s="30" t="inlineStr">
         <is>
           <t>卫星互联网实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R71" s="3" t="inlineStr">
@@ -24030,10 +24030,10 @@
       <c r="Q72" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 AIGC视觉传达实训室
 卫星互联网实训室
-空天地一体实训室
+虚拟仿真创新实训室
 人工智能应用开发实训室
 高性能智算实训室</t>
         </is>
@@ -24195,11 +24195,11 @@
       <c r="Q73" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 AIGC视觉传达实训室
 高性能智算实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R73" s="3" t="inlineStr">
@@ -24357,7 +24357,7 @@
       </c>
       <c r="Q74" s="30" t="inlineStr">
         <is>
-          <t>鸿蒙智联实训室
+          <t>鸿蒙物联网智能技术实训室
 高性能智算实训室
 人工智能应用开发实训室</t>
         </is>
@@ -24517,10 +24517,10 @@
       <c r="Q75" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 AIGC视觉传达实训室
 卫星互联网实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R75" s="3" t="inlineStr">
@@ -24681,10 +24681,10 @@
       <c r="Q76" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 高性能智算实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R76" s="7" t="inlineStr">
@@ -24843,11 +24843,11 @@
       <c r="Q77" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 AIGC视觉传达实训室
 高性能智算实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R77" s="3" t="inlineStr">
@@ -25006,7 +25006,7 @@
       </c>
       <c r="Q78" s="30" t="inlineStr">
         <is>
-          <t>鸿蒙智联实训室
+          <t>鸿蒙物联网智能技术实训室
 互联网舆情监测与管控实验室
 AIGC视觉传达实训室
 高性能智算实训室
@@ -25169,11 +25169,11 @@
       <c r="Q79" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 AIGC视觉传达实训室
 高性能智算实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R79" s="3" t="inlineStr">
@@ -25330,11 +25330,11 @@
       <c r="Q80" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 AIGC视觉传达实训室
 高性能智算实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R80" s="7" t="inlineStr">
@@ -25493,10 +25493,10 @@
       <c r="Q81" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 人工智能应用开发实训室
 高性能智算实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R81" s="3" t="inlineStr">
@@ -25655,7 +25655,7 @@
       </c>
       <c r="Q82" s="30" t="inlineStr">
         <is>
-          <t>鸿蒙智联实训室
+          <t>鸿蒙物联网智能技术实训室
 高性能智算实训室
 人工智能应用开发实训室</t>
         </is>
@@ -25819,7 +25819,7 @@
       </c>
       <c r="Q83" s="30" t="inlineStr">
         <is>
-          <t>鸿蒙智联实训室
+          <t>鸿蒙物联网智能技术实训室
 高性能智算实训室</t>
         </is>
       </c>
@@ -25987,10 +25987,10 @@
       <c r="Q84" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 AIGC视觉传达实训室
 卫星互联网实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R84" s="7" t="inlineStr">
@@ -26148,11 +26148,11 @@
       <c r="Q85" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 高性能智算实训室
 智能制造行业开发实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R85" s="3" t="inlineStr">
@@ -26314,7 +26314,7 @@
       </c>
       <c r="Q86" s="30" t="inlineStr">
         <is>
-          <t>鸿蒙智联实训室
+          <t>鸿蒙物联网智能技术实训室
 AI+网络空间安全实训室
 智能体实训室
 AIGC视觉传达实训室
@@ -26475,10 +26475,10 @@
       <c r="Q87" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 人工智能应用开发实训室
 高性能智算实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R87" s="3" t="inlineStr">
@@ -26639,12 +26639,12 @@
       <c r="Q88" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 高性能智算实训室
 AIGC视觉传达实训室
 TPU异构算力与软硬协同实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R88" s="7" t="inlineStr">
@@ -26801,7 +26801,7 @@
       </c>
       <c r="Q89" s="30" t="inlineStr">
         <is>
-          <t>鸿蒙智联实训室
+          <t>鸿蒙物联网智能技术实训室
 高性能智算实训室
 人工智能应用开发实训室</t>
         </is>
@@ -26961,12 +26961,12 @@
         <is>
           <t>低空智能实训室
 具身智能实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 AIGC视觉传达实训室
 智能交通行业应用开发实训室
 人工智能应用开发实训室
 高性能智算实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R90" s="7" t="inlineStr">
@@ -27126,12 +27126,12 @@
       </c>
       <c r="Q91" s="30" t="inlineStr">
         <is>
-          <t>鸿蒙智联实训室
+          <t>鸿蒙物联网智能技术实训室
 智能体实训室
 AIGC视觉传达实训室
 人工智能应用开发实训室
 高性能智算实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R91" s="3" t="inlineStr">
@@ -27287,7 +27287,7 @@
       </c>
       <c r="Q92" s="30" t="inlineStr">
         <is>
-          <t>鸿蒙智联实训室
+          <t>鸿蒙物联网智能技术实训室
 AIGC视觉传达实训室
 人工智能应用开发实训室
 高性能智算实训室</t>
@@ -27444,10 +27444,10 @@
       <c r="Q93" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 高性能智算实训室
 卫星互联网实训室
-空天地一体实训室
+虚拟仿真创新实训室
 人工智能应用开发实训室</t>
         </is>
       </c>
@@ -27605,11 +27605,11 @@
       <c r="Q94" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 高性能智算实训室
 AIGC视觉传达实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R94" s="7" t="inlineStr">
@@ -27769,10 +27769,10 @@
       <c r="Q95" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 人工智能应用开发实训室
 高性能智算实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R95" s="3" t="inlineStr">
@@ -27928,9 +27928,9 @@
       <c r="Q96" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 卫星互联网实训室
-空天地一体实训室
+虚拟仿真创新实训室
 人工智能应用开发实训室</t>
         </is>
       </c>
@@ -28091,12 +28091,12 @@
       <c r="Q97" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 高性能智算实训室
 AIGC视觉传达实训室
 TPU异构算力与软硬协同实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R97" s="3" t="inlineStr">
@@ -28255,9 +28255,9 @@
       <c r="Q98" s="30" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R98" s="7" t="inlineStr">
@@ -31277,7 +31277,7 @@
       <c r="Q118" s="30" t="inlineStr">
         <is>
           <t>卫星互联网实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="R118" s="7" t="inlineStr">
@@ -31587,7 +31587,7 @@
         <is>
           <t>AIGC视觉传达实训室
 卫星互联网实训室
-空天地一体实训室
+虚拟仿真创新实训室
 智能交通行业应用开发实训室
 人工智能应用开发实训室</t>
         </is>
@@ -34390,7 +34390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN242"/>
+  <dimension ref="A1:E237"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.72727272727273" defaultRowHeight="14"/>
   <cols>
     <col width="67.1454545454545" customWidth="1" style="25" min="1" max="1"/>
@@ -36829,11 +36829,6 @@
         <v>63</v>
       </c>
     </row>
-    <row r="238"/>
-    <row r="239"/>
-    <row r="240"/>
-    <row r="241"/>
-    <row r="242"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -36845,7 +36840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C27"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -36856,7 +36851,7 @@
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>25个实训室 — 师资匹配数量统计</t>
+          <t>24个实训室 — 师资匹配数量统计</t>
         </is>
       </c>
     </row>
@@ -36919,7 +36914,7 @@
     <row r="6" ht="14.5" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>空天地一体实训室</t>
+          <t>虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
@@ -36945,7 +36940,7 @@
     <row r="8" ht="14.5" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>鸿蒙智联实训室</t>
+          <t>鸿蒙物联网智能技术实训室</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
@@ -37173,26 +37168,13 @@
     <row r="26" ht="14.5" customHeight="1">
       <c r="A26" s="22" t="inlineStr">
         <is>
-          <t>洁净实验室1</t>
+          <t>洁净实验室</t>
         </is>
       </c>
       <c r="B26" s="23" t="n">
         <v>0</v>
       </c>
       <c r="C26" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>洁净实验室2</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -37615,7 +37597,7 @@
     <row r="1" ht="35" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>25个实训室 × 10个推荐方 — 师资覆盖交叉分析</t>
+          <t>24个实训室 × 10个推荐方 — 师资覆盖交叉分析</t>
         </is>
       </c>
     </row>
@@ -37798,7 +37780,7 @@
     <row r="6" ht="14.5" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>空天地一体实训室</t>
+          <t>虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
@@ -37862,7 +37844,7 @@
     <row r="8" ht="14.5" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>鸿蒙智联实训室</t>
+          <t>鸿蒙物联网智能技术实训室</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr"/>
@@ -38430,7 +38412,7 @@
 AI高端装备制造实训室
 智能制造行业开发实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="H3" s="6" t="inlineStr">
@@ -38519,12 +38501,12 @@
         <is>
           <t>低空智能实训室
 具身智能实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 AIGC视觉传达实训室
 智能交通行业应用开发实训室
 人工智能应用开发实训室
 高性能智算实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -38567,9 +38549,9 @@
           <t>具身智能实训室
 高性能智算实训室
 卫星互联网实训室
-空天地一体实训室
+虚拟仿真创新实训室
 TPU异构算力与软硬协同实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 人工智能应用开发实训室</t>
         </is>
       </c>
@@ -38613,7 +38595,7 @@
           <t>具身智能实训室
 机器视觉和VLM实训室
 AIGC视觉传达实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 高性能智算实训室
 智能交通行业应用开发实训室
 人工智能应用开发实训室</t>
@@ -38657,10 +38639,10 @@
       <c r="G8" s="10" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 AIGC视觉传达实训室
 卫星互联网实训室
-空天地一体实训室
+虚拟仿真创新实训室
 人工智能应用开发实训室
 高性能智算实训室</t>
         </is>
@@ -38703,12 +38685,12 @@
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 高性能智算实训室
 AIGC视觉传达实训室
 TPU异构算力与软硬协同实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
@@ -38749,12 +38731,12 @@
       <c r="G10" s="10" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 高性能智算实训室
 AIGC视觉传达实训室
 TPU异构算力与软硬协同实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -38798,7 +38780,7 @@
 AIGC视觉传达实训室
 AI4S实训室
 卫星互联网实训室
-空天地一体实训室
+虚拟仿真创新实训室
 人工智能应用开发实训室</t>
         </is>
       </c>
@@ -38844,7 +38826,7 @@
 电子数据取证司法鉴定实训室
 AIGC视觉传达实训室
 AI4S实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -39020,11 +39002,11 @@
       <c r="G16" s="10" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 AIGC视觉传达实训室
 高性能智算实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr">
@@ -39065,11 +39047,11 @@
       <c r="G17" s="6" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 AIGC视觉传达实训室
 高性能智算实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -39110,11 +39092,11 @@
       <c r="G18" s="10" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 AIGC视觉传达实训室
 高性能智算实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr">
@@ -39155,11 +39137,11 @@
       <c r="G19" s="6" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 AIGC视觉传达实训室
 高性能智算实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="H19" s="6" t="inlineStr">
@@ -39200,11 +39182,11 @@
       <c r="G20" s="10" t="inlineStr">
         <is>
           <t>智能边缘计算应用开发实训室
-鸿蒙智联实训室
+鸿蒙物联网智能技术实训室
 高性能智算实训室
 智能制造行业开发实训室
 人工智能应用开发实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
@@ -39244,7 +39226,7 @@
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>鸿蒙智联实训室
+          <t>鸿蒙物联网智能技术实训室
 AI+网络空间安全实训室
 智能体实训室
 AIGC视觉传达实训室
@@ -39289,12 +39271,12 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>鸿蒙智联实训室
+          <t>鸿蒙物联网智能技术实训室
 智能体实训室
 AIGC视觉传达实训室
 人工智能应用开发实训室
 高性能智算实训室
-空天地一体实训室</t>
+虚拟仿真创新实训室</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
